--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:32</t>
+    <t xml:space="preserve">2026-09-09 20:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_coquimbo.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_coquimbo.xlsx
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:33</t>
+    <t xml:space="preserve">2026-09-18 10:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
